--- a/tinHelm/excel/RoleCard.xlsx
+++ b/tinHelm/excel/RoleCard.xlsx
@@ -44,6 +44,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>解锁关卡</t>
     </r>
     <r>
@@ -581,7 +586,7 @@
     </border>
   </borders>
   <cellStyleXfs count="50">
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1287,13 +1292,13 @@
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:4">
       <c r="A6" s="1">
-        <v>3001</v>
+        <v>1</v>
       </c>
       <c r="B6" s="1">
-        <v>1001</v>
+        <v>1</v>
       </c>
       <c r="C6" s="1">
-        <v>2001</v>
+        <v>1</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -1301,13 +1306,13 @@
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:4">
       <c r="A7" s="1">
-        <v>3002</v>
+        <v>2</v>
       </c>
       <c r="B7" s="1">
-        <v>1001</v>
+        <v>1</v>
       </c>
       <c r="C7" s="1">
-        <v>2002</v>
+        <v>2</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -1315,13 +1320,13 @@
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:4">
       <c r="A8" s="1">
-        <v>3003</v>
+        <v>3</v>
       </c>
       <c r="B8" s="1">
-        <v>1001</v>
+        <v>1</v>
       </c>
       <c r="C8" s="1">
-        <v>2003</v>
+        <v>3</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -1329,13 +1334,13 @@
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:4">
       <c r="A9" s="1">
-        <v>3004</v>
+        <v>4</v>
       </c>
       <c r="B9" s="1">
-        <v>1002</v>
+        <v>2</v>
       </c>
       <c r="C9" s="1">
-        <v>2004</v>
+        <v>4</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -1343,13 +1348,13 @@
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:4">
       <c r="A10" s="1">
-        <v>3005</v>
+        <v>5</v>
       </c>
       <c r="B10" s="1">
-        <v>1002</v>
+        <v>2</v>
       </c>
       <c r="C10" s="1">
-        <v>2005</v>
+        <v>5</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -1357,13 +1362,13 @@
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:4">
       <c r="A11" s="1">
-        <v>3006</v>
+        <v>6</v>
       </c>
       <c r="B11" s="1">
-        <v>1002</v>
+        <v>2</v>
       </c>
       <c r="C11" s="1">
-        <v>2006</v>
+        <v>6</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -1371,13 +1376,13 @@
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:4">
       <c r="A12" s="1">
-        <v>3007</v>
+        <v>7</v>
       </c>
       <c r="B12" s="1">
-        <v>1003</v>
+        <v>3</v>
       </c>
       <c r="C12" s="1">
-        <v>2007</v>
+        <v>7</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -1385,13 +1390,13 @@
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:4">
       <c r="A13" s="1">
-        <v>3008</v>
+        <v>8</v>
       </c>
       <c r="B13" s="1">
-        <v>1003</v>
+        <v>3</v>
       </c>
       <c r="C13" s="1">
-        <v>2008</v>
+        <v>8</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -1399,13 +1404,13 @@
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:4">
       <c r="A14" s="1">
-        <v>3009</v>
+        <v>9</v>
       </c>
       <c r="B14" s="1">
-        <v>1003</v>
+        <v>3</v>
       </c>
       <c r="C14" s="1">
-        <v>2009</v>
+        <v>9</v>
       </c>
       <c r="D14">
         <v>0</v>
